--- a/data/Variables-used-by-LLMs.xlsx
+++ b/data/Variables-used-by-LLMs.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C043C1C7-26A7-4F9E-AE57-4BBBBF8EBB58}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC12E10-BCB1-46B1-92A2-AC1B4F8B3797}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8868" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LLM-selection" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>Task</t>
   </si>
@@ -52,6 +52,36 @@
   </si>
   <si>
     <t>meat</t>
+  </si>
+  <si>
+    <t>pick</t>
+  </si>
+  <si>
+    <t>pack</t>
+  </si>
+  <si>
+    <t>pick packer</t>
+  </si>
+  <si>
+    <t>picker</t>
+  </si>
+  <si>
+    <t>LO Operator</t>
+  </si>
+  <si>
+    <t>LO</t>
+  </si>
+  <si>
+    <t>civil labourer</t>
+  </si>
+  <si>
+    <t>production worker</t>
+  </si>
+  <si>
+    <t>production</t>
+  </si>
+  <si>
+    <t>worker</t>
   </si>
 </sst>
 </file>
@@ -474,7 +504,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -507,6 +537,56 @@
         <v>11</v>
       </c>
     </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
